--- a/1_mailing/2026_10_GBS_Lions_AI3/test.xlsx
+++ b/1_mailing/2026_10_GBS_Lions_AI3/test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cyphral/Z_Dev/Adaptive_assistant/1_mailing/2026_10_GBS_Lions_AI3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC96ABE-D540-F344-94D8-BF9BC9AD446C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD028E0F-E85A-3041-982D-84F312F93AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1120" yWindow="680" windowWidth="28380" windowHeight="18440" xr2:uid="{1D968E92-3B61-9344-970E-C8763D7F311B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>Robert</t>
   </si>
@@ -54,6 +54,12 @@
   </si>
   <si>
     <t>INVITATION | Adaptive's GBS Lions' Talks in Tricity | GBS Beyond Barriers | 08.10.2026</t>
+  </si>
+  <si>
+    <t>Katarzyna</t>
+  </si>
+  <si>
+    <t>katarzyna.szelag@adaptivesag.com</t>
   </si>
 </sst>
 </file>
@@ -925,7 +931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB2A2FC-D8BF-4F42-A279-1028F28BF1F4}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46.33203125" bestFit="1" customWidth="1"/>
@@ -956,9 +962,20 @@
         <v>5</v>
       </c>
     </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D878" xr:uid="{1DB2A2FC-D8BF-4F42-A279-1028F28BF1F4}"/>
-  <conditionalFormatting sqref="A995:A1029 A1057:A1048576 A3:A960 A1 A990:A993">
+  <conditionalFormatting sqref="A995:A1029 A1057:A1048576 A4:A960 A1 A990:A993">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
